--- a/output/pdf_financials_xlsx/DHR.H.xlsx
+++ b/output/pdf_financials_xlsx/DHR.H.xlsx
@@ -1168,7 +1168,7 @@
         <v>-2.44974</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.043904</v>
+        <v>-0.043904</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>-0.254898</v>
@@ -1420,7 +1420,7 @@
         <v>-2.44974</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.043904</v>
+        <v>-0.043904</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>-0.254898</v>
@@ -1567,7 +1567,7 @@
         <v>-2.44974</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.043904</v>
+        <v>-0.043904</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>-0.254898</v>
@@ -1805,7 +1805,7 @@
         <v>-2.44974</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.043904</v>
+        <v>-0.043904</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-0.254898</v>
@@ -1903,7 +1903,7 @@
         <v>-2.44974</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.043904</v>
+        <v>-0.043904</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-0.254898</v>
@@ -2029,7 +2029,7 @@
         <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>-0</v>
@@ -6329,19 +6329,19 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-1.133151</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.908798</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-1.224927</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.8438</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>0.985932</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>-0.037414</v>
@@ -14564,7 +14564,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E87" s="5" t="n">
         <v>0.103717</v>
       </c>
@@ -20158,7 +20162,11 @@
           <t>Write-off of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -21158,7 +21166,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E165" s="5" t="n">
         <v>-1.133151</v>
       </c>
@@ -27109,7 +27121,7 @@
         </is>
       </c>
       <c r="P235" s="5" t="n">
-        <v>0.043904</v>
+        <v>-0.043904</v>
       </c>
       <c r="Q235" s="5" t="n">
         <v>-0.254898</v>
@@ -34800,7 +34812,7 @@
         </is>
       </c>
       <c r="E326" s="5" t="n">
-        <v>0.157951</v>
+        <v>-0.157951</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -34890,7 +34902,7 @@
         </is>
       </c>
       <c r="E327" s="5" t="n">
-        <v>0.4486</v>
+        <v>-0.4486</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -36708,10 +36720,10 @@
         </is>
       </c>
       <c r="E348" s="5" t="n">
-        <v>0.326879</v>
+        <v>-0.326879</v>
       </c>
       <c r="F348" s="5" t="n">
-        <v>0.079179</v>
+        <v>-0.079179</v>
       </c>
       <c r="G348" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/DHR.H.xlsx
+++ b/output/pdf_financials_xlsx/DHR.H.xlsx
@@ -856,31 +856,31 @@
         <v>0.342645</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>0.22779</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>0.193874</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>0.161714</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.352284</v>
+        <v>0.979696</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.254788</v>
+        <v>0.311998</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>2.138956</v>
+        <v>0.310784</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.285439</v>
+        <v>0.241535</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.104392</v>
+        <v>0.35929</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.415816</v>
+        <v>0.212888</v>
       </c>
     </row>
     <row r="11">
@@ -905,31 +905,31 @@
         <v>-0.342645</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0</v>
+        <v>-0.22779</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0</v>
+        <v>-0.193874</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0</v>
+        <v>-0.161714</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.352284</v>
+        <v>-0.979696</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.254788</v>
+        <v>-0.311998</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-2.138956</v>
+        <v>-0.310784</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.285439</v>
+        <v>-0.241535</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.104392</v>
+        <v>-0.35929</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.415816</v>
+        <v>-0.212888</v>
       </c>
     </row>
     <row r="12">
@@ -939,19 +939,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000322</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.00196</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.004329</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.002941</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000534</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.002587</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000182</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -1772,19 +1772,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.428531</v>
+        <v>-3.428853</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.652579</v>
+        <v>-1.654539</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.992348</v>
+        <v>-0.996677</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-7.154928</v>
+        <v>-7.157869</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.417136</v>
+        <v>-1.41767</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.227193</v>
@@ -1796,10 +1796,10 @@
         <v>-0.198317</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.962388</v>
+        <v>-0.964975</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.351427</v>
+        <v>-0.351609</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-2.44974</v>
@@ -1870,19 +1870,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.428352</v>
+        <v>-3.428674</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.652275</v>
+        <v>-1.654235</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.992348</v>
+        <v>-0.996677</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-7.154928</v>
+        <v>-7.157869</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.417136</v>
+        <v>-1.41767</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.227193</v>
@@ -1894,10 +1894,10 @@
         <v>-0.198317</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.962388</v>
+        <v>-0.964975</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.351427</v>
+        <v>-0.351609</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-2.44974</v>
@@ -2144,31 +2144,31 @@
         <v>0.100535</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.039659</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.003372</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.00745</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.976906</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.086337</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.347262</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.08901100000000001</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.101204</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.009117999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -2242,31 +2242,31 @@
         <v>0.100535</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.039659</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.003372</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.00745</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.317629</v>
+        <v>2.294535</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.006712</v>
+        <v>1.093049</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.347262</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.08901100000000001</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.101204</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.009117999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -2830,31 +2830,31 @@
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.045145</v>
+        <v>0.005486</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.169976</v>
+        <v>0.166604</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.02905</v>
+        <v>0.0216</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.059177</v>
+        <v>0.082271</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.095331</v>
+        <v>0.008994</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.354952</v>
+        <v>0.00769</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.089951</v>
+        <v>0.00094</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.101204</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.010537</v>
+        <v>0.001419</v>
       </c>
     </row>
     <row r="49">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13950,7 +13950,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
@@ -26152,7 +26152,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -26181,31 +26181,31 @@
         </is>
       </c>
       <c r="J224" s="5" t="n">
-        <v>-0.22779</v>
+        <v>0.22779</v>
       </c>
       <c r="K224" s="5" t="n">
-        <v>-0.193874</v>
+        <v>0.193874</v>
       </c>
       <c r="L224" s="5" t="n">
-        <v>-0.161714</v>
+        <v>0.161714</v>
       </c>
       <c r="M224" s="5" t="n">
-        <v>-0.979696</v>
+        <v>0.979696</v>
       </c>
       <c r="N224" s="5" t="n">
-        <v>-0.311998</v>
+        <v>0.311998</v>
       </c>
       <c r="O224" s="5" t="n">
-        <v>-0.310784</v>
+        <v>0.310784</v>
       </c>
       <c r="P224" s="5" t="n">
-        <v>-0.241535</v>
+        <v>0.241535</v>
       </c>
       <c r="Q224" s="5" t="n">
-        <v>-0.35929</v>
+        <v>0.35929</v>
       </c>
       <c r="R224" s="5" t="n">
-        <v>-0.212888</v>
+        <v>0.212888</v>
       </c>
     </row>
     <row r="225">
@@ -28024,7 +28024,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -28460,7 +28460,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -31072,7 +31072,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -34476,7 +34476,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E322" s="5" t="n">
@@ -36458,7 +36458,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E345" s="5" t="n">

--- a/output/pdf_financials_xlsx/DHR.H.xlsx
+++ b/output/pdf_financials_xlsx/DHR.H.xlsx
@@ -1386,11 +1386,15 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>-3.428531</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>-1.652579</v>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D20" s="3" t="n">
         <v>-0.992348</v>
@@ -1436,10 +1440,10 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-0.276361</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>-0.206965</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -5937,10 +5941,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.368767</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.191482</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -5952,10 +5956,10 @@
         <v>0</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.00546</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.005795</v>
       </c>
       <c r="I110" s="3" t="n">
         <v>0</v>
@@ -5986,7 +5990,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001194</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -6212,7 +6216,7 @@
         <v>0</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.008886</v>
       </c>
       <c r="M115" s="3" t="n">
         <v>0</v>
@@ -7169,7 +7173,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001194</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -7218,7 +7222,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-1.516876</v>
+        <v>-1.51807</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.905795</v>
@@ -15576,7 +15580,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -17358,7 +17366,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -18118,7 +18130,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -18796,7 +18812,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -22604,7 +22624,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E182" s="5" t="n">
         <v>0.368767</v>
       </c>
@@ -24920,7 +24944,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E209" s="5" t="n">
         <v>-0.001194</v>
       </c>
@@ -25006,7 +25034,11 @@
           <t>Proceeds from shares issued</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E210" s="5" t="n">
         <v>0.000158</v>
       </c>
@@ -33104,7 +33136,11 @@
           <t>Loss from discontinued operations (Note 10)</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -34638,7 +34674,11 @@
           <t>Loss from discontinued operations (Note 9)</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E324" s="5" t="n">
         <v>-0.276361</v>
       </c>
